--- a/spec_links_images.xlsx
+++ b/spec_links_images.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jomar-my.sharepoint.com/personal/matt_bianchi_jomar_com/Documents/Jomar/Specification Sales/Projects/Training App/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jomar-my.sharepoint.com/personal/matt_bianchi_jomar_com/Documents/Jomar/Specification Sales/Projects/Spec Package Builder/App/Current2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B7B8E7E-9A83-42E8-BC18-3076BC9DC470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{3B7B8E7E-9A83-42E8-BC18-3076BC9DC470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04602662-D94E-4BA3-90E0-09C46DDE6C29}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4143ED1D-7BF1-4C60-8F52-57CD4B97505F}"/>
   </bookViews>
@@ -11744,7 +11744,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="\$#,##0.00_);&quot;($&quot;#,##0.00\)"/>
+    <numFmt numFmtId="164" formatCode="\$#,##0.00_);&quot;($&quot;#,##0.00\)"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -11814,7 +11814,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -11822,10 +11822,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -11835,16 +11835,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
@@ -31634,7 +31630,7 @@
         <f>IFERROR(VLOOKUP(C84,Sheet2!B:F,5,FALSE),"")</f>
         <v>Thermostatic Balancing Valve, Dezincification Resistant Lead Free Brass, Threaded Connection, Thermometer, Check Valve &amp; Dual Isolation, 150 CWP</v>
       </c>
-      <c r="E84" s="12" t="s">
+      <c r="E84" s="10" t="s">
         <v>3166</v>
       </c>
       <c r="F84" t="s">
@@ -31655,7 +31651,7 @@
         <f>IFERROR(VLOOKUP(C85,Sheet2!B:F,5,FALSE),"")</f>
         <v>Thermostatic Balancing Valve, Dezincification Resistant Lead Free Brass, Threaded Connection, Thermometer, Check Valve, Dual Isolation &amp; Integrated Strainer, 150 CWP</v>
       </c>
-      <c r="E85" s="12" t="s">
+      <c r="E85" s="10" t="s">
         <v>3173</v>
       </c>
       <c r="F85" t="s">
@@ -31676,7 +31672,7 @@
         <f>IFERROR(VLOOKUP(C86,Sheet2!B:F,5,FALSE),"")</f>
         <v>Thermostatic Balancing Valve, Dezincification Resistant Lead Free Brass, Threaded Connection, Automatic Thermal Disinfection, Thermometer, 150 CWP</v>
       </c>
-      <c r="E86" s="12" t="s">
+      <c r="E86" s="10" t="s">
         <v>3165</v>
       </c>
       <c r="F86" t="s">
@@ -31697,7 +31693,7 @@
         <f>IFERROR(VLOOKUP(C87,Sheet2!B:F,5,FALSE),"")</f>
         <v>Thermostatic Balancing Valve, Dezincification Resistant Lead Free Brass, Threaded Connection, Automatic Thermal Disinfection, Thermometer, Check Valve &amp; Dual Isolation, 150 CWP</v>
       </c>
-      <c r="E87" s="12" t="s">
+      <c r="E87" s="10" t="s">
         <v>3167</v>
       </c>
       <c r="F87" t="s">
@@ -31718,7 +31714,7 @@
         <f>IFERROR(VLOOKUP(C88,Sheet2!B:F,5,FALSE),"")</f>
         <v>Thermostatic Balancing Valve, Dezincification Resistant Lead Free Brass, Threaded Connection, Automatic Thermal Disinfection, Thermometer, Check Valve, Dual Isolation &amp; Integrated Strainer, 150 CWP</v>
       </c>
-      <c r="E88" s="12" t="s">
+      <c r="E88" s="10" t="s">
         <v>3168</v>
       </c>
       <c r="F88" t="s">
@@ -31739,7 +31735,7 @@
         <f>IFERROR(VLOOKUP(C89,Sheet2!B:F,5,FALSE),"")</f>
         <v>Thermostatic Balancing Valve, Dezincification Resistant Lead Free Brass, Threaded Connection, Axial Thermal Disinfection, with Thermometer, without Jomar Actuator, 150 CWP</v>
       </c>
-      <c r="E89" s="12" t="s">
+      <c r="E89" s="10" t="s">
         <v>3169</v>
       </c>
       <c r="F89" t="s">
@@ -31760,7 +31756,7 @@
         <f>IFERROR(VLOOKUP(C90,Sheet2!B:F,5,FALSE),"")</f>
         <v>Thermostatic Balancing Valve, Dezincification Resistant Lead Free Brass, Threaded Connection, Axial Thermal Disinfection, Thermometer, Check Valve &amp; Dual Isolation, without Jomar Actuator, 150 CWP</v>
       </c>
-      <c r="E90" s="12" t="s">
+      <c r="E90" s="10" t="s">
         <v>3170</v>
       </c>
       <c r="F90" t="s">
@@ -31781,7 +31777,7 @@
         <f>IFERROR(VLOOKUP(C91,Sheet2!B:F,5,FALSE),"")</f>
         <v>Thermostatic Balancing Valve, Dezincification Resistant Lead Free Brass, Threaded Connection, Actuated Thermal Disinfection, with Thermometer, Check Valve, Dual Isolation &amp; Integrated Strainer, 150 CWP</v>
       </c>
-      <c r="E91" s="12" t="s">
+      <c r="E91" s="10" t="s">
         <v>3171</v>
       </c>
       <c r="F91" t="s">
@@ -31825,7 +31821,7 @@
       <c r="E93" t="s">
         <v>3184</v>
       </c>
-      <c r="F93" s="12" t="s">
+      <c r="F93" s="10" t="s">
         <v>3183</v>
       </c>
     </row>
@@ -32377,11 +32373,11 @@
         <v>3215</v>
       </c>
       <c r="C120" t="s">
-        <v>228</v>
+        <v>273</v>
       </c>
       <c r="D120" t="str">
         <f>IFERROR(VLOOKUP(C120,Sheet2!B:F,5,FALSE),"")</f>
-        <v>2 Piece, Full Port, Solder Connection, Dezincification Resistant Brass, 600 WOG</v>
+        <v>2 Piece, Full Port, Solder Connection, Dezincification Resistant Brass, Stainless Steel Ball &amp; Stem, 600 WOG</v>
       </c>
       <c r="E120" t="s">
         <v>3262</v>
@@ -32398,11 +32394,11 @@
         <v>3215</v>
       </c>
       <c r="C121" t="s">
-        <v>245</v>
+        <v>287</v>
       </c>
       <c r="D121" t="str">
         <f>IFERROR(VLOOKUP(C121,Sheet2!B:F,5,FALSE),"")</f>
-        <v xml:space="preserve">2 Piece, Full Port, Solder Connection, Dezincification Resistant Brass, Latch Lock Handle, 600 WOG </v>
+        <v>2 Piece, Full Port, Solder Connection, Dezincification Reistant Brass, Stainless Steel Ball &amp; Stem, Latch Lock Handle, 600 WOG</v>
       </c>
       <c r="E121" t="s">
         <v>3263</v>
@@ -32419,11 +32415,11 @@
         <v>3215</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>301</v>
       </c>
       <c r="D122" t="str">
         <f>IFERROR(VLOOKUP(C122,Sheet2!B:F,5,FALSE),"")</f>
-        <v xml:space="preserve">2 Piece, Full Port, Solder Connection, Dezincification Resistant Brass, Thermal-Block Insulated Handle, 600 WOG </v>
+        <v>2 Piece, Full Port, Solder Connection, Dezincification Reistant Brass, Stainless Steel Ball &amp; Stem, Thermal-Block Insulated Handle, 600 WOG</v>
       </c>
       <c r="E122" t="s">
         <v>3266</v>
@@ -32932,7 +32928,7 @@
       <c r="E146" t="s">
         <v>3322</v>
       </c>
-      <c r="F146" s="12" t="s">
+      <c r="F146" s="10" t="s">
         <v>3308</v>
       </c>
     </row>
@@ -32950,7 +32946,7 @@
         <f>IFERROR(VLOOKUP(C147,Sheet2!B:F,5,FALSE),"")</f>
         <v>2 Piece, Full Port, Dezincification Resistant Lead Free Brass, Press Connection, Stainless Steel Ball &amp; Stem, Drain, 600 WOG</v>
       </c>
-      <c r="E147" s="12" t="s">
+      <c r="E147" s="10" t="s">
         <v>3323</v>
       </c>
       <c r="F147" t="s">
@@ -33223,7 +33219,7 @@
         <f>IFERROR(VLOOKUP(C160,Sheet2!B:F,5,FALSE),"")</f>
         <v>2 Piece, Standard Port, Dezincification Resistant Lead Free Brass, Press x Expansion Pex Connection, Stainless Steel Ball &amp; Stem, 250 WOG</v>
       </c>
-      <c r="E160" s="12" t="s">
+      <c r="E160" s="10" t="s">
         <v>3350</v>
       </c>
       <c r="F160" t="s">
@@ -37522,7 +37518,7 @@
       <c r="E367" t="s">
         <v>3897</v>
       </c>
-      <c r="F367" s="12" t="s">
+      <c r="F367" s="10" t="s">
         <v>3891</v>
       </c>
     </row>
@@ -37573,7 +37569,7 @@
   <dimension ref="A1:H2112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="37.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -37581,7 +37577,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -37602,7 +37598,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -37623,7 +37619,7 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -37644,7 +37640,7 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -37665,7 +37661,7 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -37686,7 +37682,7 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -37707,7 +37703,7 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -37728,7 +37724,7 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -37749,7 +37745,7 @@
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -37770,7 +37766,7 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -37791,7 +37787,7 @@
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -37812,7 +37808,7 @@
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -37833,7 +37829,7 @@
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -37854,7 +37850,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -37875,7 +37871,7 @@
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -37896,7 +37892,7 @@
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -37917,7 +37913,7 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -37938,7 +37934,7 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -37959,7 +37955,7 @@
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -37980,7 +37976,7 @@
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -38001,7 +37997,7 @@
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -38022,7 +38018,7 @@
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -38043,7 +38039,7 @@
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -38064,7 +38060,7 @@
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -38085,7 +38081,7 @@
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -38106,7 +38102,7 @@
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -38127,7 +38123,7 @@
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -38148,7 +38144,7 @@
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -38169,7 +38165,7 @@
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -38190,7 +38186,7 @@
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -38211,7 +38207,7 @@
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -38232,7 +38228,7 @@
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -38253,7 +38249,7 @@
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -38274,7 +38270,7 @@
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -38295,7 +38291,7 @@
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -38316,7 +38312,7 @@
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -38337,7 +38333,7 @@
       </c>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -38358,7 +38354,7 @@
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -38379,7 +38375,7 @@
       </c>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="10" t="s">
+      <c r="A39" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -38400,7 +38396,7 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -38421,7 +38417,7 @@
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -38442,7 +38438,7 @@
       </c>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -38463,7 +38459,7 @@
       </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -38484,7 +38480,7 @@
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -38505,7 +38501,7 @@
       </c>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -38526,7 +38522,7 @@
       </c>
     </row>
     <row r="46" spans="1:6">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -38547,7 +38543,7 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -38568,7 +38564,7 @@
       </c>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -38589,7 +38585,7 @@
       </c>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -38610,7 +38606,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="10" t="s">
+      <c r="A50" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -38631,7 +38627,7 @@
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="10" t="s">
+      <c r="A51" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -38652,7 +38648,7 @@
       </c>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="10" t="s">
+      <c r="A52" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B52" s="1" t="s">
@@ -38673,7 +38669,7 @@
       </c>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="10" t="s">
+      <c r="A53" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B53" s="1" t="s">
@@ -38694,7 +38690,7 @@
       </c>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="10" t="s">
+      <c r="A54" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -38715,7 +38711,7 @@
       </c>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="10" t="s">
+      <c r="A55" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -38736,7 +38732,7 @@
       </c>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="10" t="s">
+      <c r="A56" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B56" s="1" t="s">
@@ -38757,7 +38753,7 @@
       </c>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="10" t="s">
+      <c r="A57" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B57" s="1" t="s">
@@ -38778,7 +38774,7 @@
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="10" t="s">
+      <c r="A58" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B58" s="1" t="s">
@@ -38799,7 +38795,7 @@
       </c>
     </row>
     <row r="59" spans="1:6">
-      <c r="A59" s="10" t="s">
+      <c r="A59" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -38820,7 +38816,7 @@
       </c>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="10" t="s">
+      <c r="A60" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B60" s="1" t="s">
@@ -38841,7 +38837,7 @@
       </c>
     </row>
     <row r="61" spans="1:6">
-      <c r="A61" s="10" t="s">
+      <c r="A61" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B61" s="1" t="s">
@@ -38862,7 +38858,7 @@
       </c>
     </row>
     <row r="62" spans="1:6">
-      <c r="A62" s="10" t="s">
+      <c r="A62" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B62" s="1" t="s">
@@ -38883,7 +38879,7 @@
       </c>
     </row>
     <row r="63" spans="1:6">
-      <c r="A63" s="10" t="s">
+      <c r="A63" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -38904,7 +38900,7 @@
       </c>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="10" t="s">
+      <c r="A64" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B64" s="1" t="s">
@@ -38925,7 +38921,7 @@
       </c>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="10" t="s">
+      <c r="A65" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B65" s="1" t="s">
@@ -38946,7 +38942,7 @@
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="10" t="s">
+      <c r="A66" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B66" s="1" t="s">
@@ -38967,7 +38963,7 @@
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="10" t="s">
+      <c r="A67" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B67" s="1" t="s">
@@ -38988,7 +38984,7 @@
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="10" t="s">
+      <c r="A68" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B68" s="1" t="s">
@@ -39009,7 +39005,7 @@
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="10" t="s">
+      <c r="A69" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B69" s="1" t="s">
@@ -39030,7 +39026,7 @@
       </c>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="10" t="s">
+      <c r="A70" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B70" s="1" t="s">
@@ -39051,7 +39047,7 @@
       </c>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="10" t="s">
+      <c r="A71" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -39072,7 +39068,7 @@
       </c>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="10" t="s">
+      <c r="A72" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B72" s="1" t="s">
@@ -39093,7 +39089,7 @@
       </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="10" t="s">
+      <c r="A73" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B73" s="1" t="s">
@@ -39114,7 +39110,7 @@
       </c>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="10" t="s">
+      <c r="A74" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B74" s="1" t="s">
@@ -39135,7 +39131,7 @@
       </c>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="10" t="s">
+      <c r="A75" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B75" s="1" t="s">
@@ -39156,7 +39152,7 @@
       </c>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="10" t="s">
+      <c r="A76" s="1" t="s">
         <v>3105</v>
       </c>
       <c r="B76" s="1" t="s">
@@ -45504,7 +45500,7 @@
       </c>
     </row>
     <row r="381" spans="1:6">
-      <c r="A381" s="11" t="s">
+      <c r="A381" t="s">
         <v>3106</v>
       </c>
       <c r="B381" t="s">
@@ -45525,7 +45521,7 @@
       </c>
     </row>
     <row r="382" spans="1:6">
-      <c r="A382" s="11" t="s">
+      <c r="A382" t="s">
         <v>3106</v>
       </c>
       <c r="B382" t="s">
@@ -50091,7 +50087,7 @@
       </c>
     </row>
     <row r="600" spans="1:6">
-      <c r="A600" s="11" t="s">
+      <c r="A600" t="s">
         <v>3110</v>
       </c>
       <c r="B600" t="s">
@@ -50112,7 +50108,7 @@
       </c>
     </row>
     <row r="601" spans="1:6">
-      <c r="A601" s="11" t="s">
+      <c r="A601" t="s">
         <v>3110</v>
       </c>
       <c r="B601" t="s">
@@ -50133,7 +50129,7 @@
       </c>
     </row>
     <row r="602" spans="1:6">
-      <c r="A602" s="11" t="s">
+      <c r="A602" t="s">
         <v>3110</v>
       </c>
       <c r="B602" t="s">
@@ -50154,7 +50150,7 @@
       </c>
     </row>
     <row r="603" spans="1:6">
-      <c r="A603" s="11" t="s">
+      <c r="A603" t="s">
         <v>3110</v>
       </c>
       <c r="B603" t="s">
@@ -50175,7 +50171,7 @@
       </c>
     </row>
     <row r="604" spans="1:6">
-      <c r="A604" s="11" t="s">
+      <c r="A604" t="s">
         <v>3110</v>
       </c>
       <c r="B604" t="s">
@@ -50196,7 +50192,7 @@
       </c>
     </row>
     <row r="605" spans="1:6">
-      <c r="A605" s="11" t="s">
+      <c r="A605" t="s">
         <v>3110</v>
       </c>
       <c r="B605" t="s">
@@ -50217,7 +50213,7 @@
       </c>
     </row>
     <row r="606" spans="1:6">
-      <c r="A606" s="11" t="s">
+      <c r="A606" t="s">
         <v>3110</v>
       </c>
       <c r="B606" t="s">
@@ -50238,7 +50234,7 @@
       </c>
     </row>
     <row r="607" spans="1:6">
-      <c r="A607" s="11" t="s">
+      <c r="A607" t="s">
         <v>3110</v>
       </c>
       <c r="B607" t="s">
@@ -50259,7 +50255,7 @@
       </c>
     </row>
     <row r="608" spans="1:6">
-      <c r="A608" s="11" t="s">
+      <c r="A608" t="s">
         <v>3110</v>
       </c>
       <c r="B608" t="s">
@@ -50280,7 +50276,7 @@
       </c>
     </row>
     <row r="609" spans="1:6">
-      <c r="A609" s="11" t="s">
+      <c r="A609" t="s">
         <v>3110</v>
       </c>
       <c r="B609" t="s">
@@ -50301,7 +50297,7 @@
       </c>
     </row>
     <row r="610" spans="1:6">
-      <c r="A610" s="11" t="s">
+      <c r="A610" t="s">
         <v>3110</v>
       </c>
       <c r="B610" t="s">
@@ -50322,7 +50318,7 @@
       </c>
     </row>
     <row r="611" spans="1:6">
-      <c r="A611" s="11" t="s">
+      <c r="A611" t="s">
         <v>3110</v>
       </c>
       <c r="B611" t="s">
@@ -50343,7 +50339,7 @@
       </c>
     </row>
     <row r="612" spans="1:6">
-      <c r="A612" s="11" t="s">
+      <c r="A612" t="s">
         <v>3110</v>
       </c>
       <c r="B612" t="s">
@@ -50364,7 +50360,7 @@
       </c>
     </row>
     <row r="613" spans="1:6">
-      <c r="A613" s="11" t="s">
+      <c r="A613" t="s">
         <v>3110</v>
       </c>
       <c r="B613" t="s">
@@ -50385,7 +50381,7 @@
       </c>
     </row>
     <row r="614" spans="1:6">
-      <c r="A614" s="11" t="s">
+      <c r="A614" t="s">
         <v>3110</v>
       </c>
       <c r="B614" t="s">
@@ -50406,7 +50402,7 @@
       </c>
     </row>
     <row r="615" spans="1:6">
-      <c r="A615" s="11" t="s">
+      <c r="A615" t="s">
         <v>3110</v>
       </c>
       <c r="B615" t="s">
@@ -50427,7 +50423,7 @@
       </c>
     </row>
     <row r="616" spans="1:6">
-      <c r="A616" s="11" t="s">
+      <c r="A616" t="s">
         <v>3110</v>
       </c>
       <c r="B616" t="s">
@@ -50448,7 +50444,7 @@
       </c>
     </row>
     <row r="617" spans="1:6">
-      <c r="A617" s="11" t="s">
+      <c r="A617" t="s">
         <v>3110</v>
       </c>
       <c r="B617" t="s">
@@ -50469,7 +50465,7 @@
       </c>
     </row>
     <row r="618" spans="1:6">
-      <c r="A618" s="11" t="s">
+      <c r="A618" t="s">
         <v>3110</v>
       </c>
       <c r="B618" t="s">
@@ -50490,7 +50486,7 @@
       </c>
     </row>
     <row r="619" spans="1:6">
-      <c r="A619" s="11" t="s">
+      <c r="A619" t="s">
         <v>3110</v>
       </c>
       <c r="B619" t="s">
